--- a/data/trans_camb/IQ2601_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IQ2601_R2-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-12,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17,99</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,83</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-7,46</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,95</t>
+          <t>17,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -2,82</t>
+          <t>-12,71; 6,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 11,73</t>
+          <t>5,05; 23,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 30,37</t>
+          <t>0,78; 32,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 8,02</t>
+          <t>-22,85; -2,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 24,02</t>
+          <t>-9,61; 10,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 31,86</t>
+          <t>3,43; 30,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,94; -0,29</t>
+          <t>-14,3; -0,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 15,0</t>
+          <t>0,19; 15,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 26,45</t>
+          <t>6,1; 27,26</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-5,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-21,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-5,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28,37%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,7; -5,38</t>
+          <t>-23,18; 13,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 21,19</t>
+          <t>9,04; 52,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 54,8</t>
+          <t>1,8; 69,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 17,64</t>
+          <t>-34,98; -4,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 53,17</t>
+          <t>-14,69; 19,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 67,39</t>
+          <t>6,01; 55,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -0,62</t>
+          <t>-24,77; -0,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 29,44</t>
+          <t>0,3; 28,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 51,02</t>
+          <t>11,05; 52,36</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-14,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,23</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,02</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-9,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,62</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-14,81</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,56</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,6</t>
+          <t>10,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,8; -2,08</t>
+          <t>-22,22; -7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 13,4</t>
+          <t>-4,13; 10,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 17,01</t>
+          <t>4,99; 25,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,73; -7,41</t>
+          <t>-17,61; -0,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 10,22</t>
+          <t>-1,6; 13,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 26,29</t>
+          <t>-13,03; 15,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,47; -6,55</t>
+          <t>-17,14; -7,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 9,31</t>
+          <t>-0,52; 9,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 19,85</t>
+          <t>2,19; 19,03</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-22,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-14,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-22,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,38; -3,76</t>
+          <t>-32,95; -12,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 22,58</t>
+          <t>-5,96; 17,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 28,03</t>
+          <t>7,68; 41,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,6; -12,27</t>
+          <t>-26,68; -1,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 16,86</t>
+          <t>-2,33; 22,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 42,44</t>
+          <t>-19,48; 25,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,73; -10,71</t>
+          <t>-26,08; -11,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 15,12</t>
+          <t>-0,79; 15,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 31,86</t>
+          <t>3,62; 30,9</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-25,23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-13,05</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-14,18</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-24,71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-18,71</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-25,23</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-13,05</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-14,68</t>
+          <t>-5,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-9,83</t>
+          <t>-10,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,08; -16,74</t>
+          <t>-33,35; -16,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -9,9</t>
+          <t>-20,82; -4,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 9,68</t>
+          <t>-30,74; -0,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,38; -16,71</t>
+          <t>-33,23; -16,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -5,54</t>
+          <t>-27,67; -10,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,61; -0,49</t>
+          <t>-23,03; 8,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,3; -19,33</t>
+          <t>-30,51; -18,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,35; -9,7</t>
+          <t>-22,05; -10,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,71; -0,04</t>
+          <t>-21,66; -1,34</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-32,14%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-16,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-18,07%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-31,39%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-23,76%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-3,27%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-32,14%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-16,63%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-18,71%</t>
+          <t>-7,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-12,5%</t>
+          <t>-13,79%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,28; -22,04</t>
+          <t>-40,9; -22,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,75; -13,46</t>
+          <t>-25,88; -6,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 12,85</t>
+          <t>-38,6; -0,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,17; -22,35</t>
+          <t>-41,01; -21,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,66; -7,42</t>
+          <t>-33,69; -14,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,35; -0,77</t>
+          <t>-27,96; 11,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,47; -25,36</t>
+          <t>-37,87; -25,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,54; -12,66</t>
+          <t>-27,42; -13,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,5; -0,06</t>
+          <t>-27,32; -1,65</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-21,93</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,48</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,92</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-16,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-6,26</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-21,93</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-8,48</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>-9,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>-0,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,61; -8,03</t>
+          <t>-29,7; -13,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 1,49</t>
+          <t>-16,49; -0,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 6,43</t>
+          <t>-7,34; 18,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-30,03; -13,9</t>
+          <t>-24,25; -7,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -0,19</t>
+          <t>-13,78; 2,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 19,42</t>
+          <t>-22,47; 3,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,55; -13,53</t>
+          <t>-24,99; -13,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -1,58</t>
+          <t>-13,0; -2,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 9,52</t>
+          <t>-10,71; 8,34</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-32,26%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-12,47%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-23,9%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-8,94%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-10,36%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-32,26%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-12,47%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>-13,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>-0,81%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,5; -12,21</t>
+          <t>-42,29; -20,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 2,23</t>
+          <t>-22,9; -0,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 9,31</t>
+          <t>-10,33; 28,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,12; -21,61</t>
+          <t>-33,45; -12,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,64; -0,4</t>
+          <t>-18,89; 3,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 29,64</t>
+          <t>-31,96; 5,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,35; -20,2</t>
+          <t>-34,92; -20,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -2,69</t>
+          <t>-17,96; -3,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 13,93</t>
+          <t>-15,52; 11,96</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-16,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,99</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-15,36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,8</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-16,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>4,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -11,26</t>
+          <t>-20,58; -12,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,15</t>
+          <t>-5,01; 3,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 8,7</t>
+          <t>0,87; 14,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -12,2</t>
+          <t>-19,6; -11,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,84</t>
+          <t>-8,2; 0,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 14,08</t>
+          <t>-6,94; 7,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -12,95</t>
+          <t>-18,82; -12,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,65</t>
+          <t>-5,35; 0,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,47</t>
+          <t>-0,49; 9,43</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-24,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,61%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,63%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-5,6%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-24,97%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-1,61%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -16,81</t>
+          <t>-30,86; -19,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 0,22</t>
+          <t>-7,59; 4,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 12,95</t>
+          <t>1,61; 22,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -19,09</t>
+          <t>-28,01; -17,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 4,52</t>
+          <t>-11,64; 0,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,18; 22,01</t>
+          <t>-10,14; 10,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,63; -19,71</t>
+          <t>-27,66; -19,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,99</t>
+          <t>-7,92; 0,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,3</t>
+          <t>-0,72; 14,41</t>
         </is>
       </c>
     </row>
